--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI22"/>
+  <dimension ref="A1:AI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46013.65625</v>
+        <v>46013.625</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46013.66666666666</v>
+        <v>46013.65625</v>
       </c>
     </row>
     <row r="16">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46013.6875</v>
+        <v>46013.66666666666</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46013.70833333334</v>
+        <v>46013.6875</v>
       </c>
     </row>
     <row r="19">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46013.73958333334</v>
+        <v>46013.70833333334</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46013.79166666666</v>
+        <v>46013.73958333334</v>
       </c>
     </row>
     <row r="22">
@@ -2998,116 +2998,235 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Molynes United</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3" t="n">
+        <v>46013.79166666666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Racing United</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Harbour View</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="3" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3" t="n">
         <v>46013.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46013.58333333334</v>
+        <v>46013.625</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46013.58333333334</v>
+        <v>46013.625</v>
       </c>
     </row>
     <row r="12">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46013.625</v>
+        <v>46013.65625</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46013.625</v>
+        <v>46013.66666666666</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46013.65625</v>
+        <v>46013.66666666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46013.66666666666</v>
+        <v>46013.6875</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46013.66666666666</v>
+        <v>46013.70833333334</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46013.6875</v>
+        <v>46013.70833333334</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46013.70833333334</v>
+        <v>46013.73958333334</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46013.70833333334</v>
+        <v>46013.79166666666</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -2989,244 +2989,6 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46013.73958333334</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46013</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Molynes United</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="3" t="n">
-        <v>46013.79166666666</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46013</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Racing United</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Harbour View</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="3" t="n">
         <v>46013.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI21"/>
+  <dimension ref="A1:AI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46013.625</v>
+        <v>46013.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46013.625</v>
+        <v>46013.58333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46013.65625</v>
+        <v>46013.625</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46013.66666666666</v>
+        <v>46013.625</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46013.66666666666</v>
+        <v>46013.65625</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46013.6875</v>
+        <v>46013.66666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46013.70833333334</v>
+        <v>46013.66666666666</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46013.70833333334</v>
+        <v>46013.6875</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46013.73958333334</v>
+        <v>46013.70833333334</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46013.79166666666</v>
+        <v>46013.70833333334</v>
       </c>
     </row>
     <row r="21">
@@ -2879,116 +2879,354 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3" t="n">
+        <v>46013.73958333334</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Molynes United</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3" t="n">
+        <v>46013.79166666666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Racing United</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Harbour View</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="3" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3" t="n">
         <v>46013.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>7.5</v>
+        <v>1.73</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1.29</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>7.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.73</v>
+        <v>7.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.73</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>8.9</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>1.22</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>8.9</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,90 +523,25 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>HT_Odd_Over25</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>HT_Odd_Under25</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>FT_Odd_Over05</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over15</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under15</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over25</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under25</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over35</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under35</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_Yes</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_No</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_D</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_A_D</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -688,46 +623,7 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="3" t="n">
+      <c r="V2" s="3" t="n">
         <v>46013.22916666666</v>
       </c>
     </row>
@@ -807,46 +703,7 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="3" t="n">
+      <c r="V3" s="3" t="n">
         <v>46013.375</v>
       </c>
     </row>
@@ -926,46 +783,7 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="3" t="n">
+      <c r="V4" s="3" t="n">
         <v>46013.41666666666</v>
       </c>
     </row>
@@ -1045,46 +863,7 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="3" t="n">
+      <c r="V5" s="3" t="n">
         <v>46013.45833333334</v>
       </c>
     </row>
@@ -1164,46 +943,7 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="3" t="n">
+      <c r="V6" s="3" t="n">
         <v>46013.52083333334</v>
       </c>
     </row>
@@ -1272,10 +1012,10 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1283,46 +1023,7 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="3" t="n">
+      <c r="V7" s="3" t="n">
         <v>46013.54166666666</v>
       </c>
     </row>
@@ -1337,7 +1038,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1048,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1074,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1402,46 +1103,7 @@
       <c r="U8" t="n">
         <v>0</v>
       </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="3" t="n">
+      <c r="V8" s="3" t="n">
         <v>46013.58333333334</v>
       </c>
     </row>
@@ -1456,7 +1118,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1128,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1521,46 +1183,7 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="3" t="n">
+      <c r="V9" s="3" t="n">
         <v>46013.58333333334</v>
       </c>
     </row>
@@ -1575,7 +1198,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1208,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1234,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1629,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1640,46 +1263,7 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="3" t="n">
+      <c r="V10" s="3" t="n">
         <v>46013.58333333334</v>
       </c>
     </row>
@@ -1759,46 +1343,7 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="3" t="n">
+      <c r="V11" s="3" t="n">
         <v>46013.58333333334</v>
       </c>
     </row>
@@ -1878,46 +1423,7 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="3" t="n">
+      <c r="V12" s="3" t="n">
         <v>46013.625</v>
       </c>
     </row>
@@ -1932,7 +1438,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1448,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1474,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>8.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1986,10 +1492,10 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1997,46 +1503,7 @@
       <c r="U13" t="n">
         <v>0</v>
       </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="3" t="n">
+      <c r="V13" s="3" t="n">
         <v>46013.625</v>
       </c>
     </row>
@@ -2051,7 +1518,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +1528,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +1554,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.22</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>8.9</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2116,46 +1583,7 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="n">
+      <c r="V14" s="3" t="n">
         <v>46013.625</v>
       </c>
     </row>
@@ -2224,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -2235,46 +1663,7 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="3" t="n">
+      <c r="V15" s="3" t="n">
         <v>46013.65625</v>
       </c>
     </row>
@@ -2299,12 +1688,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2354,46 +1743,7 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="3" t="n">
+      <c r="V16" s="3" t="n">
         <v>46013.66666666666</v>
       </c>
     </row>
@@ -2418,12 +1768,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2473,46 +1823,7 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="3" t="n">
+      <c r="V17" s="3" t="n">
         <v>46013.66666666666</v>
       </c>
     </row>
@@ -2592,46 +1903,7 @@
       <c r="U18" t="n">
         <v>0</v>
       </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="3" t="n">
+      <c r="V18" s="3" t="n">
         <v>46013.6875</v>
       </c>
     </row>
@@ -2700,10 +1972,10 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2711,46 +1983,7 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="3" t="n">
+      <c r="V19" s="3" t="n">
         <v>46013.70833333334</v>
       </c>
     </row>
@@ -2830,46 +2063,7 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="3" t="n">
+      <c r="V20" s="3" t="n">
         <v>46013.70833333334</v>
       </c>
     </row>
@@ -2938,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2949,46 +2143,7 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="3" t="n">
+      <c r="V21" s="3" t="n">
         <v>46013.73958333334</v>
       </c>
     </row>
@@ -3068,46 +2223,7 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="3" t="n">
+      <c r="V22" s="3" t="n">
         <v>46013.79166666666</v>
       </c>
     </row>
@@ -3187,46 +2303,7 @@
       <c r="U23" t="n">
         <v>0</v>
       </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="3" t="n">
+      <c r="V23" s="3" t="n">
         <v>46013.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:AI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,25 +523,90 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>HT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over15</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under15</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over25</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under15</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over35</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under35</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_H_D</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_A_D</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -623,7 +688,46 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>46013.22916666666</v>
       </c>
     </row>
@@ -703,7 +807,46 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
         <v>46013.375</v>
       </c>
     </row>
@@ -783,7 +926,46 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
         <v>46013.41666666666</v>
       </c>
     </row>
@@ -863,7 +1045,46 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>46013.45833333334</v>
       </c>
     </row>
@@ -943,7 +1164,46 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
         <v>46013.52083333334</v>
       </c>
     </row>
@@ -1012,18 +1272,57 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1.75</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AB7" t="n">
         <v>1.95</v>
       </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>46013.54166666666</v>
       </c>
     </row>
@@ -1038,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1048,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1074,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1103,7 +1402,46 @@
       <c r="U8" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
       </c>
     </row>
@@ -1118,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1128,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1154,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1183,7 +1521,46 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
       </c>
     </row>
@@ -1198,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1208,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1234,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1252,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1263,7 +1640,46 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
       </c>
     </row>
@@ -1278,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1288,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1314,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1343,7 +1759,46 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
         <v>46013.58333333334</v>
       </c>
     </row>
@@ -1358,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1368,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1394,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1423,7 +1878,46 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
         <v>46013.625</v>
       </c>
     </row>
@@ -1492,18 +1986,57 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.8</v>
       </c>
-      <c r="S13" t="n">
+      <c r="AB13" t="n">
         <v>1.9</v>
       </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="3" t="n">
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
         <v>46013.625</v>
       </c>
     </row>
@@ -1518,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1528,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1554,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1583,7 +2116,46 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="n">
         <v>46013.625</v>
       </c>
     </row>
@@ -1652,18 +2224,57 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.78</v>
       </c>
-      <c r="S15" t="n">
+      <c r="AB15" t="n">
         <v>1.92</v>
       </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3" t="n">
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n">
         <v>46013.65625</v>
       </c>
     </row>
@@ -1688,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1743,7 +2354,46 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
       </c>
     </row>
@@ -1768,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1823,7 +2473,46 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
       </c>
     </row>
@@ -1903,7 +2592,46 @@
       <c r="U18" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3" t="n">
         <v>46013.6875</v>
       </c>
     </row>
@@ -1972,18 +2700,57 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2</v>
       </c>
-      <c r="S19" t="n">
+      <c r="AB19" t="n">
         <v>1.8</v>
       </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="3" t="n">
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
       </c>
     </row>
@@ -2063,7 +2830,46 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
       </c>
     </row>
@@ -2132,18 +2938,57 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1.7</v>
       </c>
-      <c r="S21" t="n">
+      <c r="AB21" t="n">
         <v>2.02</v>
       </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="3" t="n">
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
       </c>
     </row>
@@ -2223,7 +3068,46 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3" t="n">
         <v>46013.79166666666</v>
       </c>
     </row>
@@ -2303,7 +3187,46 @@
       <c r="U23" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3" t="n">
         <v>46013.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46013.41666666666</v>
+        <v>46013.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46013.45833333334</v>
+        <v>46013.52083333334</v>
       </c>
     </row>
     <row r="6">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46013.52083333334</v>
+        <v>46013.54166666666</v>
       </c>
     </row>
     <row r="7">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.1</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>8.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46013.54166666666</v>
+        <v>46013.58333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46013.58333333334</v>
+        <v>46013.625</v>
       </c>
     </row>
     <row r="12">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.22</v>
+        <v>9</v>
       </c>
       <c r="M14" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="N14" t="n">
-        <v>8.9</v>
+        <v>1.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46013.625</v>
+        <v>46013.65625</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46013.65625</v>
+        <v>46013.66666666666</v>
       </c>
     </row>
     <row r="16">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46013.66666666666</v>
+        <v>46013.6875</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46013.6875</v>
+        <v>46013.70833333334</v>
       </c>
     </row>
     <row r="19">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46013.70833333334</v>
+        <v>46013.73958333334</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46013.73958333334</v>
+        <v>46013.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46013.79166666666</v>
+        <v>46013.875</v>
       </c>
     </row>
     <row r="23">

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>8.9</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>8.9</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>8.9</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>8.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>8.9</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>8.9</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>5.4</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>8.9</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>8.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>8.9</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>8.9</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,76 +2920,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46013.79166666666</v>
+        <v>46013.73958333334</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46013.875</v>
+        <v>46013.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3117,116 +3117,235 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3" t="n">
+        <v>46013.875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Racing United</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Harbour View</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="3" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="n">
         <v>46013.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>8.9</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>8.9</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>8.9</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>8.9</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="N13" t="n">
         <v>1.75</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.93</v>
+        <v>3.85</v>
       </c>
       <c r="O21" t="n">
         <v>2.31</v>
@@ -2968,7 +2968,7 @@
         <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
         <v>3</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -668,64 +668,64 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46013.22916666666</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46013.375</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46013.45833333334</v>
@@ -1144,40 +1144,40 @@
         <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="n">
         <v>1.75</v>
@@ -1186,22 +1186,22 @@
         <v>1.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46013.54166666666</v>
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.75</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>3.6</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.49</v>
+        <v>4.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T7" t="n">
-        <v>2.43</v>
+        <v>2.77</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>2.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.25</v>
+        <v>2.58</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4</v>
+        <v>3.19</v>
       </c>
       <c r="T8" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.67</v>
       </c>
-      <c r="V8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z9" t="n">
         <v>3.8</v>
       </c>
-      <c r="N9" t="n">
+      <c r="AA9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.75</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.18</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AH10" t="n">
         <v>3.6</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1278,7 +1278,7 @@
         <v>2.77</v>
       </c>
       <c r="T7" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
         <v>1.38</v>
@@ -1293,7 +1293,7 @@
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
         <v>3.15</v>
@@ -1317,10 +1317,10 @@
         <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q8" t="n">
         <v>4</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.58</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6.7</v>
+        <v>6.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
         <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.49</v>
+        <v>1.65</v>
       </c>
       <c r="P9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.11</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.43</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>6.15</v>
+        <v>4.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.8</v>
+        <v>5.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>3.6</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.25</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>3.19</v>
       </c>
       <c r="T10" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.67</v>
       </c>
-      <c r="V10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>5.4</v>
+        <v>3.33</v>
       </c>
       <c r="N11" t="n">
-        <v>8.9</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>8.9</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2096,40 +2096,40 @@
         <v>1.35</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
         <v>1.78</v>
@@ -2138,22 +2138,22 @@
         <v>1.92</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46013.65625</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2691,40 +2691,40 @@
         <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA19" t="n">
         <v>2</v>
@@ -2733,22 +2733,22 @@
         <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2810,40 +2810,40 @@
         <v>10</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.7</v>
@@ -2852,22 +2852,22 @@
         <v>2.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.73958333334</v>
@@ -2929,7 +2929,7 @@
         <v>3.85</v>
       </c>
       <c r="O21" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
         <v>2.2</v>
@@ -2938,7 +2938,7 @@
         <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
         <v>2.73</v>
@@ -2947,7 +2947,7 @@
         <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
         <v>7.5</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -674,7 +674,7 @@
         <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
@@ -689,7 +689,7 @@
         <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W2" t="n">
         <v>1.09</v>
@@ -698,19 +698,19 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
         <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB2" t="n">
         <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AD2" t="n">
         <v>1.44</v>
@@ -722,10 +722,10 @@
         <v>2.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46013.22916666666</v>
@@ -778,25 +778,25 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.39</v>
+        <v>4.4</v>
       </c>
       <c r="M3" t="n">
         <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="O3" t="n">
         <v>4.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
         <v>3.14</v>
@@ -808,7 +808,7 @@
         <v>1.47</v>
       </c>
       <c r="V3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="W3" t="n">
         <v>1.08</v>
@@ -826,13 +826,13 @@
         <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
         <v>2.49</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE3" t="n">
         <v>1.73</v>
@@ -841,10 +841,10 @@
         <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46013.375</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1150,7 +1150,7 @@
         <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
         <v>1.37</v>
@@ -1177,7 +1177,7 @@
         <v>1.24</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AA6" t="n">
         <v>1.75</v>
@@ -1192,10 +1192,10 @@
         <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
         <v>1.25</v>
@@ -1272,7 +1272,7 @@
         <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
         <v>2.77</v>
@@ -1293,10 +1293,10 @@
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
         <v>1.8</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O8" t="n">
-        <v>2.49</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.33</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG8" t="n">
         <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.65</v>
+        <v>2.49</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.25</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.11</v>
+        <v>2.43</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>4.1</v>
+        <v>6.15</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH10" t="n">
         <v>3.6</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3.33</v>
+        <v>5.4</v>
       </c>
       <c r="N11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.75</v>
       </c>
-      <c r="O11" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.15</v>
+        <v>3.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>8.9</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2.4</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.63</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="T13" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2108,7 +2108,7 @@
         <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.01</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
         <v>2.77</v>
@@ -2117,7 +2117,7 @@
         <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="W14" t="n">
         <v>1.05</v>
@@ -2147,7 +2147,7 @@
         <v>2.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
         <v>1.2</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2831,7 +2831,7 @@
         <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
         <v>1.07</v>
@@ -2840,7 +2840,7 @@
         <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
         <v>3.9</v>
@@ -2861,13 +2861,13 @@
         <v>2.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.73958333334</v>
@@ -2944,10 +2944,10 @@
         <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
         <v>7.5</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -897,40 +897,40 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M4" t="n">
-        <v>4.09</v>
+        <v>3.94</v>
       </c>
       <c r="N4" t="n">
-        <v>4.28</v>
+        <v>4.36</v>
       </c>
       <c r="O4" t="n">
         <v>2.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
         <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="T4" t="n">
         <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V4" t="n">
         <v>5.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
         <v>1.03</v>
@@ -939,19 +939,19 @@
         <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>3.96</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
         <v>2.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
         <v>1.65</v>
@@ -960,7 +960,7 @@
         <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
         <v>2.05</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O7" t="n">
-        <v>4.5</v>
+        <v>1.65</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>2.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>8.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>2.77</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>2.09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="V7" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>5.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE7" t="n">
         <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="M8" t="n">
         <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q8" t="n">
         <v>2.58</v>
@@ -1394,40 +1394,40 @@
         <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.19</v>
+        <v>2.94</v>
       </c>
       <c r="T8" t="n">
         <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" t="n">
         <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
         <v>1.67</v>
@@ -1436,10 +1436,10 @@
         <v>2.05</v>
       </c>
       <c r="AG8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.49</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T9" t="n">
-        <v>2.43</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.65</v>
+        <v>2.49</v>
       </c>
       <c r="P10" t="n">
-        <v>2.67</v>
+        <v>2.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.1</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.09</v>
+        <v>2.43</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>4.1</v>
+        <v>6.15</v>
       </c>
       <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.21</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Z10" t="n">
-        <v>5.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>8.9</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>2.23</v>
+        <v>2.79</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.79</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>3.19</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>8.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="P12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC12" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.19</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>3.75</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
         <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AH18" t="n">
         <v>2</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="O20" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="P20" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="T20" t="n">
-        <v>2.57</v>
+        <v>2.94</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.73958333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="T21" t="n">
-        <v>2.94</v>
+        <v>2.57</v>
       </c>
       <c r="U21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.36</v>
       </c>
-      <c r="V21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q8" t="n">
         <v>4</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.58</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U8" t="n">
         <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6.6</v>
+        <v>6.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
         <v>3.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AB8" t="n">
         <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AD8" t="n">
         <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O10" t="n">
-        <v>2.49</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T10" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
         <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>6.15</v>
+        <v>6.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
         <v>3.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
         <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AD10" t="n">
         <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46013.65625</v>
+        <v>46013.64583333334</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.59</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
-        <v>2.33</v>
+        <v>2.77</v>
       </c>
       <c r="U15" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>5.05</v>
+        <v>6.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.38</v>
+        <v>3.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.4</v>
+        <v>1.52</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46013.66666666666</v>
+        <v>46013.65625</v>
       </c>
     </row>
     <row r="16">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.33</v>
+        <v>2.59</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="O16" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="U16" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="V16" t="n">
-        <v>4.45</v>
+        <v>5.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.19</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.8</v>
+        <v>4.33</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>1.72</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46013.6875</v>
+        <v>46013.66666666666</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,76 +2563,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46013.70833333334</v>
+        <v>46013.6875</v>
       </c>
     </row>
     <row r="19">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
         <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="AH19" t="n">
         <v>2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,76 +2801,76 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.8</v>
       </c>
-      <c r="M20" t="n">
+      <c r="AC20" t="n">
         <v>3.4</v>
       </c>
-      <c r="N20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46013.73958333334</v>
+        <v>46013.70833333334</v>
       </c>
     </row>
     <row r="21">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46013.79166666666</v>
+        <v>46013.73958333334</v>
       </c>
     </row>
     <row r="23">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46013.875</v>
+        <v>46013.79166666666</v>
       </c>
     </row>
     <row r="24">

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.7</v>
+        <v>4.52</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
         <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46013.52083333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.67</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.1</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>2.77</v>
       </c>
       <c r="T7" t="n">
-        <v>2.09</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.55</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
         <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>1.65</v>
       </c>
       <c r="P9" t="n">
-        <v>2.06</v>
+        <v>2.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>8.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>2.77</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>2.09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>5.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
         <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2.4</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.75</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.79</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
-        <v>4.94</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
         <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="P20" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
         <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="AH20" t="n">
         <v>2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="O21" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>2.57</v>
+        <v>2.94</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="T22" t="n">
-        <v>2.94</v>
+        <v>2.57</v>
       </c>
       <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.36</v>
       </c>
-      <c r="V22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.52</v>
+        <v>4.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
         <v>1.75</v>
@@ -1061,10 +1061,10 @@
         <v>2.81</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
         <v>3.92</v>
@@ -1150,7 +1150,7 @@
         <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
         <v>1.37</v>
@@ -1159,10 +1159,10 @@
         <v>2.85</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
         <v>6.15</v>
@@ -1177,7 +1177,7 @@
         <v>1.24</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="n">
         <v>1.75</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O7" t="n">
-        <v>4.5</v>
+        <v>1.65</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>2.77</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>2.09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>5.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.49</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T8" t="n">
-        <v>2.43</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>3.58</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>8.5</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.67</v>
+        <v>2.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.1</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.67</v>
       </c>
-      <c r="V9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q10" t="n">
         <v>4</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.58</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U10" t="n">
         <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>6.6</v>
+        <v>6.15</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" t="n">
         <v>3.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AB10" t="n">
         <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AD10" t="n">
         <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
-        <v>4.94</v>
+        <v>2.86</v>
       </c>
       <c r="P11" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>3.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V11" t="n">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD11" t="n">
         <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>5.4</v>
+        <v>3.33</v>
       </c>
       <c r="N12" t="n">
-        <v>8.9</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.65</v>
+        <v>4.84</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>2.37</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="V12" t="n">
-        <v>4.9</v>
+        <v>6.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.79</v>
+        <v>3.42</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>2.86</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.75</v>
+        <v>1.16</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>8.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="P13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.19</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>3.78</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2230,7 +2230,7 @@
         <v>2.81</v>
       </c>
       <c r="T15" t="n">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="U15" t="n">
         <v>1.39</v>
@@ -2248,7 +2248,7 @@
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
         <v>1.78</v>
@@ -2260,7 +2260,7 @@
         <v>3.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
         <v>2.2</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.59</v>
+        <v>4.33</v>
       </c>
       <c r="M16" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.33</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.33</v>
+        <v>2.59</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N17" t="n">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="O17" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="U17" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="V17" t="n">
-        <v>4.45</v>
+        <v>5.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.19</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
         <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="AH19" t="n">
         <v>2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
         <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2944,7 +2944,7 @@
         <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="U21" t="n">
         <v>1.36</v>
@@ -2971,7 +2971,7 @@
         <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AD21" t="n">
         <v>1.29</v>
@@ -2983,10 +2983,10 @@
         <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3069,7 +3069,7 @@
         <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="W22" t="n">
         <v>1.07</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -674,16 +674,16 @@
         <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
         <v>1.5</v>
@@ -704,16 +704,16 @@
         <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB2" t="n">
         <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="n">
         <v>1.67</v>
@@ -725,7 +725,7 @@
         <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46013.22916666666</v>
@@ -778,40 +778,40 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="O3" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
         <v>3.14</v>
       </c>
       <c r="T3" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
         <v>1.03</v>
@@ -820,13 +820,13 @@
         <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
         <v>2.49</v>
@@ -838,13 +838,13 @@
         <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG3" t="n">
         <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46013.375</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
         <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>5.48</v>
+        <v>5.59</v>
       </c>
       <c r="P5" t="n">
         <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="R5" t="n">
         <v>1.44</v>
@@ -1040,10 +1040,10 @@
         <v>2.46</v>
       </c>
       <c r="T5" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
         <v>8.699999999999999</v>
@@ -1055,34 +1055,34 @@
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>3.92</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG5" t="n">
         <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46013.52083333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>3.8</v>
       </c>
       <c r="M7" t="n">
-        <v>5.3</v>
+        <v>3.44</v>
       </c>
       <c r="N7" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.5</v>
+        <v>2.36</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>2.77</v>
       </c>
       <c r="T7" t="n">
-        <v>2.09</v>
+        <v>2.77</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.55</v>
+        <v>3.28</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.6</v>
+        <v>1.17</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z8" t="n">
         <v>3.8</v>
       </c>
-      <c r="N8" t="n">
+      <c r="AA8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.75</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.2</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.58</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>9.85</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>1.65</v>
       </c>
       <c r="P9" t="n">
-        <v>2.13</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>1.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.9</v>
+        <v>2.06</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O10" t="n">
-        <v>2.49</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T10" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
         <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>6.15</v>
+        <v>6.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
         <v>3.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
         <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AD10" t="n">
         <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>8.9</v>
       </c>
       <c r="O11" t="n">
-        <v>2.86</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.52</v>
+        <v>6.38</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.79</v>
+        <v>2.29</v>
       </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>6.7</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>3.78</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4</v>
+        <v>3.33</v>
       </c>
       <c r="N13" t="n">
-        <v>8.9</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.38</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.29</v>
+        <v>2.73</v>
       </c>
       <c r="U13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.57</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>3.78</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
         <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2920,16 +2920,16 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="P21" t="n">
         <v>2.2</v>
@@ -2941,13 +2941,13 @@
         <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="T21" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V21" t="n">
         <v>7.5</v>
@@ -2968,7 +2968,7 @@
         <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
         <v>3.4</v>
@@ -2983,10 +2983,10 @@
         <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="M4" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.36</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.3</v>
@@ -924,34 +924,34 @@
         <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V4" t="n">
         <v>5.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
         <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE4" t="n">
         <v>1.65</v>
@@ -960,10 +960,10 @@
         <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46013.45833333334</v>
@@ -1135,43 +1135,43 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.1</v>
+        <v>5.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="O6" t="n">
-        <v>5.5</v>
+        <v>4.69</v>
       </c>
       <c r="P6" t="n">
         <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
         <v>1.24</v>
@@ -1180,19 +1180,19 @@
         <v>3.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC6" t="n">
         <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
         <v>1.95</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="O8" t="n">
-        <v>2.49</v>
+        <v>1.65</v>
       </c>
       <c r="P8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.11</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.43</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>6.15</v>
+        <v>4.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.78</v>
+        <v>2.06</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="M9" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>9.85</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.65</v>
+        <v>4.07</v>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.390000000000001</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2</v>
+        <v>6.55</v>
       </c>
       <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.21</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>3.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.6</v>
+        <v>1.24</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
         <v>4</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.58</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U10" t="n">
         <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AB10" t="n">
         <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="M11" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N11" t="n">
-        <v>8.9</v>
+        <v>7.6</v>
       </c>
       <c r="O11" t="n">
         <v>1.65</v>
@@ -1745,46 +1745,46 @@
         <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.38</v>
+        <v>9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="U11" t="n">
         <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
         <v>1.95</v>
@@ -1793,10 +1793,10 @@
         <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="O12" t="n">
-        <v>4.84</v>
+        <v>4.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="R12" t="n">
         <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="U12" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>6.35</v>
+        <v>6.55</v>
       </c>
       <c r="W12" t="n">
         <v>1.05</v>
@@ -1888,16 +1888,16 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>2.86</v>
@@ -1906,16 +1906,16 @@
         <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>2.9</v>
@@ -1992,16 +1992,16 @@
         <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="U13" t="n">
         <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
@@ -2010,13 +2010,13 @@
         <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>3.1</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2221,22 +2221,22 @@
         <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="U15" t="n">
         <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
@@ -2245,31 +2245,31 @@
         <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
         <v>1.08</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z16" t="n">
         <v>4.33</v>
       </c>
-      <c r="M16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="O16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AA16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.19</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.59</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.37</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.33</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.78</v>
+        <v>2.45</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>2.92</v>
       </c>
       <c r="O19" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
         <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.48</v>
+        <v>2.91</v>
       </c>
       <c r="AA20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2920,16 +2920,16 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.93</v>
+        <v>3.85</v>
       </c>
       <c r="O21" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
         <v>2.2</v>
@@ -2941,13 +2941,13 @@
         <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="T21" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
         <v>7.5</v>
@@ -2968,7 +2968,7 @@
         <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
         <v>3.4</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="O22" t="n">
         <v>1.81</v>
@@ -3063,13 +3063,13 @@
         <v>3.04</v>
       </c>
       <c r="T22" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
         <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
         <v>1.07</v>
@@ -3081,25 +3081,25 @@
         <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC22" t="n">
         <v>2.72</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
         <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG22" t="n">
         <v>1.18</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1016,43 +1016,43 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
         <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>5.59</v>
+        <v>5.7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="T5" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
         <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
         <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
         <v>1.36</v>
@@ -1061,25 +1061,25 @@
         <v>2.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AD5" t="n">
         <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
         <v>1.12</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>4.5</v>
+        <v>4.07</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="T7" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>6.4</v>
+        <v>6.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.28</v>
+        <v>3.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.2</v>
       </c>
-      <c r="M8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N8" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="O8" t="n">
+      <c r="Z8" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.65</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>4.07</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>6.55</v>
+        <v>6.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.62</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.49</v>
+        <v>1.65</v>
       </c>
       <c r="P10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="AD10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.11</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>7.6</v>
+        <v>1.87</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>4.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>2.27</v>
       </c>
       <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.25</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AH11" t="n">
-        <v>3.68</v>
+        <v>1.19</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="N12" t="n">
-        <v>1.87</v>
+        <v>7.6</v>
       </c>
       <c r="O12" t="n">
-        <v>4.25</v>
+        <v>1.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.27</v>
+        <v>9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>2.89</v>
+        <v>3.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.72</v>
+        <v>2.23</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>6.55</v>
+        <v>4.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.34</v>
+        <v>4.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.86</v>
+        <v>2.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.19</v>
+        <v>3.68</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.59</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.34</v>
+        <v>1.55</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.82</v>
+        <v>2.15</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="U16" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>2.59</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="N17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.55</v>
       </c>
-      <c r="O17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.65</v>
-      </c>
       <c r="V17" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="n">
         <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.45</v>
+        <v>1.81</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE19" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AH19" t="n">
         <v>2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.59</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.81</v>
       </c>
-      <c r="M20" t="n">
+      <c r="AC20" t="n">
         <v>3.4</v>
       </c>
-      <c r="N20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="AD20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="N21" t="n">
-        <v>3.85</v>
+        <v>8.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="R21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.38</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.92</v>
+        <v>3.1</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>8.5</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="T22" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH22" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -668,28 +668,28 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="V2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
         <v>1.09</v>
@@ -701,19 +701,19 @@
         <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AB2" t="n">
         <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
         <v>1.67</v>
@@ -725,7 +725,7 @@
         <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46013.22916666666</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>5.58</v>
       </c>
       <c r="M3" t="n">
         <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="O3" t="n">
         <v>5</v>
@@ -793,7 +793,7 @@
         <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
@@ -811,7 +811,7 @@
         <v>5.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
         <v>1.03</v>
@@ -820,28 +820,28 @@
         <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
         <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="n">
         <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>2.06</v>
       </c>
       <c r="AH3" t="n">
         <v>1.15</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="M4" t="n">
         <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4.32</v>
       </c>
       <c r="O4" t="n">
         <v>2.2</v>
@@ -915,10 +915,10 @@
         <v>4.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="T4" t="n">
         <v>2.4</v>
@@ -927,43 +927,43 @@
         <v>1.49</v>
       </c>
       <c r="V4" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
         <v>4.2</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.64</v>
       </c>
-      <c r="AB4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AF4" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46013.45833333334</v>
@@ -1025,40 +1025,40 @@
         <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>5.7</v>
+        <v>5.61</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AA5" t="n">
         <v>2.17</v>
@@ -1067,22 +1067,22 @@
         <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46013.52083333334</v>
@@ -1135,61 +1135,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.25</v>
+        <v>6.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>4.69</v>
+        <v>6.05</v>
       </c>
       <c r="P6" t="n">
         <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T6" t="n">
         <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
         <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
         <v>1.85</v>
@@ -1254,28 +1254,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
         <v>2.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="T7" t="n">
         <v>2.5</v>
@@ -1284,16 +1284,16 @@
         <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>6.55</v>
+        <v>6.1</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
         <v>3.62</v>
@@ -1302,25 +1302,25 @@
         <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF7" t="n">
         <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.49</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.29</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z8" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AF8" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.75</v>
       </c>
-      <c r="O9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>3.09</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.65</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.3</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.87</v>
+        <v>8.9</v>
       </c>
       <c r="O11" t="n">
-        <v>4.25</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
+        <v>9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.27</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.72</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="V11" t="n">
-        <v>6.55</v>
+        <v>4.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.34</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
         <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.86</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.19</v>
+        <v>3.78</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>5.8</v>
+        <v>3.33</v>
       </c>
       <c r="N12" t="n">
-        <v>7.6</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.65</v>
+        <v>4.05</v>
       </c>
       <c r="P12" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>2.23</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="U12" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.68</v>
+        <v>1.19</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1980,10 +1980,10 @@
         <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="R13" t="n">
         <v>1.38</v>
@@ -1998,10 +1998,10 @@
         <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
@@ -2010,7 +2010,7 @@
         <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA13" t="n">
         <v>1.85</v>
@@ -2028,13 +2028,13 @@
         <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2227,7 +2227,7 @@
         <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="T15" t="n">
         <v>2.63</v>
@@ -2239,7 +2239,7 @@
         <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1.05</v>
@@ -2248,13 +2248,13 @@
         <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AC15" t="n">
         <v>3.12</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>2.59</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="N16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.55</v>
       </c>
-      <c r="O16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.65</v>
-      </c>
       <c r="V16" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.59</v>
+        <v>3.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.82</v>
+        <v>2.15</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="T17" t="n">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V19" t="n">
-        <v>8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>3.59</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.45</v>
+        <v>1.81</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.4</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z20" t="n">
-        <v>3.44</v>
+        <v>2.91</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF20" t="n">
+      <c r="AH20" t="n">
         <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.59</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="N21" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="O21" t="n">
         <v>1.81</v>
@@ -2947,7 +2947,7 @@
         <v>2.45</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V21" t="n">
         <v>6</v>
@@ -2965,10 +2965,10 @@
         <v>3.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC21" t="n">
         <v>2.72</v>
@@ -2980,7 +2980,7 @@
         <v>2.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
         <v>1.18</v>
@@ -3060,7 +3060,7 @@
         <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T22" t="n">
         <v>2.65</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z8" t="n">
         <v>3.8</v>
       </c>
-      <c r="N8" t="n">
+      <c r="AA8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.75</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.32</v>
-      </c>
-      <c r="M9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>3.09</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.49</v>
+        <v>1.65</v>
       </c>
       <c r="P10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>3.09</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="O21" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH21" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="R22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.38</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.92</v>
+        <v>3.1</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -668,28 +668,28 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
         <v>2.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="U2" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.09</v>
@@ -701,16 +701,16 @@
         <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB2" t="n">
         <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AD2" t="n">
         <v>1.44</v>
@@ -722,10 +722,10 @@
         <v>2.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46013.22916666666</v>
@@ -787,10 +787,10 @@
         <v>1.47</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>4.56</v>
       </c>
       <c r="P3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
         <v>1.97</v>
@@ -826,7 +826,7 @@
         <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
         <v>2.46</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.7</v>
+        <v>4.52</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="O5" t="n">
         <v>5.61</v>
@@ -1034,10 +1034,10 @@
         <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="T5" t="n">
         <v>3.5</v>
@@ -1061,22 +1061,22 @@
         <v>2.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AD5" t="n">
         <v>1.12</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
         <v>1.27</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="T7" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.49</v>
+        <v>1.65</v>
       </c>
       <c r="P8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>3.09</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,28 +1492,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
         <v>4</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.58</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
         <v>2.5</v>
@@ -1525,40 +1525,40 @@
         <v>6.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AD9" t="n">
         <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>2.73</v>
       </c>
       <c r="T10" t="n">
-        <v>2.06</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.09</v>
+        <v>1.17</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>8.9</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>3.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>3.55</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="V11" t="n">
-        <v>4.8</v>
+        <v>6.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.78</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>8.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>1.65</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.64</v>
+        <v>9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="V13" t="n">
-        <v>6.75</v>
+        <v>4.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>3.78</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.59</v>
+        <v>3.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>1.68</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.82</v>
+        <v>2.15</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="T16" t="n">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="U16" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.8</v>
+        <v>2.59</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="N17" t="n">
-        <v>1.68</v>
+        <v>2.29</v>
       </c>
       <c r="O17" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.15</v>
+        <v>2.82</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.19</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="M4" t="n">
         <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="P4" t="n">
         <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
@@ -939,13 +939,13 @@
         <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AA4" t="n">
         <v>1.69</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AC4" t="n">
         <v>2.73</v>
@@ -957,7 +957,7 @@
         <v>1.64</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AG4" t="n">
         <v>1.22</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.52</v>
+        <v>4.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
         <v>5.61</v>
@@ -1061,10 +1061,10 @@
         <v>2.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
         <v>4.65</v>
@@ -1144,25 +1144,25 @@
         <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>6.05</v>
+        <v>4.69</v>
       </c>
       <c r="P6" t="n">
         <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
         <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="T6" t="n">
         <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V6" t="n">
         <v>6.15</v>
@@ -1201,7 +1201,7 @@
         <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46013.54166666666</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="M7" t="n">
         <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="O7" t="n">
         <v>4</v>
@@ -1296,25 +1296,25 @@
         <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="AA7" t="n">
         <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD7" t="n">
         <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AG7" t="n">
         <v>1.25</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.65</v>
+        <v>2.49</v>
       </c>
       <c r="P8" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>2.67</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>4.2</v>
+        <v>6.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.5</v>
+        <v>3.84</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>3.09</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.49</v>
+        <v>1.65</v>
       </c>
       <c r="P9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1623,7 +1623,7 @@
         <v>4.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="Q10" t="n">
         <v>2.3</v>
@@ -1632,7 +1632,7 @@
         <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T10" t="n">
         <v>2.77</v>
@@ -1674,7 +1674,7 @@
         <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
         <v>1.17</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>8.9</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.64</v>
+        <v>9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>6.75</v>
+        <v>4.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>3.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
-        <v>4.05</v>
+        <v>2.9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.23</v>
+        <v>3.64</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="U12" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="V12" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.61</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.19</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>3.61</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>8.9</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.65</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>9</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.78</v>
+        <v>1.19</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2224,22 +2224,22 @@
         <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
         <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.05</v>
@@ -2248,7 +2248,7 @@
         <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AA15" t="n">
         <v>1.78</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.8</v>
+        <v>2.59</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="N16" t="n">
-        <v>1.68</v>
+        <v>2.29</v>
       </c>
       <c r="O16" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.15</v>
+        <v>2.82</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="T16" t="n">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
       <c r="U16" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="V16" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.19</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.59</v>
+        <v>3.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.29</v>
+        <v>1.68</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.82</v>
+        <v>2.15</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="T17" t="n">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2700,10 +2700,10 @@
         <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T19" t="n">
         <v>2.8</v>
@@ -2724,7 +2724,7 @@
         <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
         <v>2</v>
@@ -2733,7 +2733,7 @@
         <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="AD19" t="n">
         <v>1.25</v>
@@ -2745,7 +2745,7 @@
         <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH19" t="n">
         <v>1.58</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
         <v>1.04</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.92</v>
+        <v>3.1</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="T22" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH22" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -668,22 +668,22 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
         <v>1.51</v>
@@ -692,7 +692,7 @@
         <v>5.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>1.03</v>
@@ -701,7 +701,7 @@
         <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA2" t="n">
         <v>1.54</v>
@@ -722,10 +722,10 @@
         <v>2.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46013.22916666666</v>
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.58</v>
+        <v>4.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N3" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="O3" t="n">
-        <v>4.56</v>
+        <v>5.72</v>
       </c>
       <c r="P3" t="n">
         <v>2.3</v>
@@ -802,13 +802,13 @@
         <v>3.14</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U3" t="n">
         <v>1.48</v>
       </c>
       <c r="V3" t="n">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="W3" t="n">
         <v>1.08</v>
@@ -820,19 +820,19 @@
         <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="AA3" t="n">
         <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
         <v>2.46</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE3" t="n">
         <v>1.73</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="M4" t="n">
         <v>4</v>
@@ -906,13 +906,13 @@
         <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="P4" t="n">
         <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.68</v>
+        <v>4.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
@@ -930,7 +930,7 @@
         <v>5.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
         <v>1.04</v>
@@ -939,13 +939,13 @@
         <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
         <v>2.73</v>
@@ -960,7 +960,7 @@
         <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
         <v>2.12</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
         <v>4.69</v>
@@ -1150,40 +1150,40 @@
         <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.14</v>
+        <v>2.69</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="U6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>6.15</v>
+        <v>6.65</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
         <v>3.1</v>
@@ -1192,7 +1192,7 @@
         <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
         <v>1.95</v>
@@ -1201,7 +1201,7 @@
         <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46013.54166666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.58</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
         <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB7" t="n">
         <v>1.95</v>
       </c>
       <c r="AC7" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AD7" t="n">
         <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.49</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="T8" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.32</v>
-      </c>
-      <c r="M9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>1.65</v>
       </c>
       <c r="P10" t="n">
-        <v>2.07</v>
+        <v>2.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>2.77</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.77</v>
+        <v>2.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>5.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>3.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="V11" t="n">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB12" t="n">
         <v>2.4</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.61</v>
+        <v>3.78</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1968,67 +1968,67 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="O13" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="U13" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AG13" t="n">
         <v>1.21</v>
@@ -2209,10 +2209,10 @@
         <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2227,16 +2227,16 @@
         <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="T15" t="n">
         <v>2.77</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
@@ -2251,10 +2251,10 @@
         <v>3.24</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
         <v>3.12</v>
@@ -2263,16 +2263,16 @@
         <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46013.65625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.59</v>
+        <v>4.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>1.68</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.82</v>
+        <v>2.16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T16" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="U17" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.19</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="N18" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="P19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE19" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB20" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.15</v>
+        <v>3.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.89</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>3.94</v>
       </c>
       <c r="O21" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.72</v>
+        <v>3.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="T22" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>5.9</v>
       </c>
       <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.04</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.4</v>
+        <v>2.71</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.92</v>
+        <v>3.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.7</v>
+        <v>4.52</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O5" t="n">
         <v>5.61</v>
@@ -1037,10 +1037,10 @@
         <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U5" t="n">
         <v>1.29</v>
@@ -1061,22 +1061,22 @@
         <v>2.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AD5" t="n">
         <v>1.12</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
         <v>1.27</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="O7" t="n">
-        <v>2.49</v>
+        <v>1.65</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.95</v>
-      </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>2.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="V7" t="n">
-        <v>6.15</v>
+        <v>4.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.78</v>
+        <v>2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z8" t="n">
         <v>3.8</v>
       </c>
-      <c r="N8" t="n">
+      <c r="AA8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.75</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,37 +1492,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.5</v>
+        <v>4.47</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.31</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
@@ -1531,34 +1531,34 @@
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.32</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>1.76</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>2.21</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="V11" t="n">
-        <v>6.7</v>
+        <v>5.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1</v>
+        <v>2.46</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3.4</v>
       </c>
-      <c r="N13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.21</v>
-      </c>
       <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.29</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="V16" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T17" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>2.92</v>
       </c>
       <c r="O19" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="T19" t="n">
-        <v>3.36</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="P20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE20" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.89</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.94</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.4</v>
       </c>
-      <c r="V21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.31</v>
+        <v>1.89</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>3.94</v>
       </c>
       <c r="O22" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
         <v>7.5</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.9</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.71</v>
+        <v>3.35</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.3</v>
+        <v>1.91</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="M7" t="n">
-        <v>6.18</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>9.85</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.1</v>
+        <v>2.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3.26</v>
       </c>
       <c r="T7" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.6</v>
+        <v>1.32</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="O8" t="n">
-        <v>2.49</v>
+        <v>1.65</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S8" t="n">
         <v>4</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.95</v>
-      </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>2.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>6.15</v>
+        <v>4.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.78</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
         <v>4</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.58</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.26</v>
+        <v>2.95</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U10" t="n">
         <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB10" t="n">
         <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AD10" t="n">
         <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
         <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S11" t="n">
         <v>3.3</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.12</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="V11" t="n">
-        <v>5.45</v>
+        <v>4.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.19</v>
+        <v>3.78</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>3.3</v>
       </c>
       <c r="M12" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>7.6</v>
+        <v>1.76</v>
       </c>
       <c r="O12" t="n">
-        <v>1.65</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>2.21</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="U12" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8</v>
+        <v>5.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.78</v>
+        <v>1.19</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1974,7 +1974,7 @@
         <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>2.9</v>
@@ -1995,7 +1995,7 @@
         <v>2.55</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
         <v>6.7</v>
@@ -2007,22 +2007,22 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
         <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
         <v>1.7</v>
@@ -2224,10 +2224,10 @@
         <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
         <v>2.77</v>
@@ -2260,19 +2260,19 @@
         <v>3.12</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
         <v>2.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
         <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46013.65625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T16" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="U17" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2700,10 +2700,10 @@
         <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="T19" t="n">
         <v>2.8</v>
@@ -2715,10 +2715,10 @@
         <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
         <v>1.3</v>
@@ -2733,7 +2733,7 @@
         <v>1.82</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AD19" t="n">
         <v>1.25</v>
@@ -2801,19 +2801,19 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
         <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="P20" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
         <v>4.75</v>
@@ -2822,25 +2822,25 @@
         <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="T20" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
         <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
         <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
         <v>2.91</v>
@@ -2849,10 +2849,10 @@
         <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
         <v>1.18</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="O21" t="n">
         <v>1.78</v>
@@ -2959,7 +2959,7 @@
         <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
         <v>4</v>
@@ -2968,7 +2968,7 @@
         <v>1.71</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC21" t="n">
         <v>2.71</v>
@@ -2977,7 +2977,7 @@
         <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AF21" t="n">
         <v>1.7</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
         <v>2.38</v>
@@ -3060,19 +3060,19 @@
         <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="T22" t="n">
         <v>2.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>6.85</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
@@ -3087,7 +3087,7 @@
         <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
         <v>3.35</v>
@@ -3102,7 +3102,7 @@
         <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
         <v>1.91</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.52</v>
+        <v>4.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
         <v>5.61</v>
@@ -1040,16 +1040,16 @@
         <v>2.33</v>
       </c>
       <c r="T5" t="n">
-        <v>3.48</v>
+        <v>3.09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
         <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
@@ -1061,10 +1061,10 @@
         <v>2.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
         <v>4.7</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.58</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.26</v>
+        <v>2.95</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
         <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB7" t="n">
         <v>1.95</v>
       </c>
       <c r="AC7" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AD7" t="n">
         <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
         <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>6.18</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>9.85</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2.93</v>
       </c>
       <c r="T8" t="n">
-        <v>2.11</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.23</v>
       </c>
       <c r="AE8" t="n">
         <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.6</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.47</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>3.44</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.79</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
         <v>4.5</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.7</v>
-      </c>
       <c r="T9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB9" t="n">
         <v>2.62</v>
       </c>
-      <c r="U9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC9" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
         <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>3.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.49</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>2.95</v>
+        <v>3.26</v>
       </c>
       <c r="T10" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
         <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
         <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
         <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AG10" t="n">
         <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2209,10 +2209,10 @@
         <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2251,10 +2251,10 @@
         <v>3.24</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AC15" t="n">
         <v>3.12</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="V16" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T17" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.48</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE19" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AF19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH19" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>2.92</v>
       </c>
       <c r="O20" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.06</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>9.109999999999999</v>
+        <v>3.85</v>
       </c>
       <c r="O21" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>5.9</v>
+        <v>6.85</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.71</v>
+        <v>3.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.3</v>
+        <v>1.91</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>6.85</v>
+        <v>5.9</v>
       </c>
       <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.04</v>
       </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.35</v>
+        <v>2.71</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,37 +1373,37 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>2.93</v>
+        <v>3.26</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.08</v>
@@ -1412,34 +1412,34 @@
         <v>1</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>2.93</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.75</v>
+        <v>3.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="AE9" t="n">
         <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.6</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.5</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH10" t="n">
         <v>3.6</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.32</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>5.5</v>
+        <v>3.33</v>
       </c>
       <c r="N11" t="n">
-        <v>7.6</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>2.34</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="T11" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="U11" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="V11" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.78</v>
+        <v>1.19</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.3</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.76</v>
+        <v>8.9</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>1.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.21</v>
+        <v>9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="V12" t="n">
-        <v>5.45</v>
+        <v>4.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.19</v>
+        <v>3.75</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T16" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="U17" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V19" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE20" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AF20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="V21" t="n">
-        <v>6.85</v>
+        <v>5.9</v>
       </c>
       <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
         <v>1.04</v>
       </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.35</v>
+        <v>2.71</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="T22" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>5.9</v>
+        <v>6.85</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.71</v>
+        <v>3.35</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.3</v>
+        <v>1.91</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O2" t="n">
         <v>5.5</v>
@@ -674,22 +674,22 @@
         <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
         <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V2" t="n">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
@@ -698,34 +698,34 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AB2" t="n">
         <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE2" t="n">
         <v>1.67</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.14</v>
+        <v>2.38</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46013.22916666666</v>
@@ -778,25 +778,25 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="M3" t="n">
         <v>4.2</v>
       </c>
       <c r="N3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="O3" t="n">
-        <v>5.72</v>
+        <v>5.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
         <v>3.14</v>
@@ -808,7 +808,7 @@
         <v>1.48</v>
       </c>
       <c r="V3" t="n">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="W3" t="n">
         <v>1.08</v>
@@ -820,16 +820,16 @@
         <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB3" t="n">
         <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD3" t="n">
         <v>1.5</v>
@@ -838,13 +838,13 @@
         <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG3" t="n">
         <v>2.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46013.375</v>
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="P4" t="n">
         <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.5</v>
+        <v>3.77</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
@@ -930,7 +930,7 @@
         <v>5.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
         <v>1.04</v>
@@ -939,7 +939,7 @@
         <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="AA4" t="n">
         <v>1.65</v>
@@ -954,16 +954,16 @@
         <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AF4" t="n">
         <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46013.45833333334</v>
@@ -1025,40 +1025,40 @@
         <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>5.61</v>
+        <v>5.43</v>
       </c>
       <c r="P5" t="n">
         <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="T5" t="n">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AA5" t="n">
         <v>2.17</v>
@@ -1067,22 +1067,22 @@
         <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AD5" t="n">
         <v>1.12</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
         <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46013.52083333334</v>
@@ -1135,61 +1135,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>4.69</v>
+        <v>6.1</v>
       </c>
       <c r="P6" t="n">
         <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="U6" t="n">
         <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.12</v>
+        <v>3.39</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
         <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
         <v>1.75</v>
@@ -1201,7 +1201,7 @@
         <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46013.54166666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>2.49</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
         <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>6.15</v>
+        <v>6.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
         <v>1.95</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.5</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2</v>
       </c>
-      <c r="O8" t="n">
-        <v>4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.32</v>
+        <v>2.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1507,16 +1507,16 @@
         <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
         <v>1.38</v>
@@ -1525,16 +1525,16 @@
         <v>6.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
         <v>1.8</v>
@@ -1546,7 +1546,7 @@
         <v>3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
         <v>1.75</v>
@@ -1555,7 +1555,7 @@
         <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
         <v>1.17</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>3.34</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>3.44</v>
       </c>
       <c r="O10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.65</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>2.91</v>
       </c>
       <c r="P11" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.28</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1861,16 +1861,16 @@
         <v>1.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>6.86</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
         <v>2.27</v>
@@ -1879,19 +1879,19 @@
         <v>1.58</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="W12" t="n">
         <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.65</v>
+        <v>4.79</v>
       </c>
       <c r="AA12" t="n">
         <v>1.8</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.4</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.55</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>6.7</v>
+        <v>5.55</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.68</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2096,64 +2096,64 @@
         <v>6.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46013.64583333334</v>
@@ -2230,13 +2230,13 @@
         <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
@@ -2248,7 +2248,7 @@
         <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
         <v>1.78</v>
@@ -2269,7 +2269,7 @@
         <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
         <v>1.08</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>4.4</v>
+        <v>2.87</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>2.96</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="V16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.5</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AG17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH19" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="W20" t="n">
         <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.91</v>
+        <v>3.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="O21" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="T21" t="n">
         <v>2.45</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>5.9</v>
+        <v>6.85</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.71</v>
+        <v>3.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>6.85</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.04</v>
       </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.35</v>
+        <v>2.71</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46013.79166666666</v>
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46013.89583333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>3.34</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>3.44</v>
       </c>
       <c r="O8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.65</v>
       </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S9" t="n">
         <v>4.5</v>
       </c>
-      <c r="P9" t="n">
+      <c r="T9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
         <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>2.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.96</v>
+        <v>4.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.44</v>
+        <v>1.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.49</v>
+        <v>4.5</v>
       </c>
       <c r="P10" t="n">
         <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T10" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
         <v>1.8</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>5.4</v>
+        <v>3.33</v>
       </c>
       <c r="N12" t="n">
-        <v>8.9</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.65</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.86</v>
+        <v>2.37</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="T12" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>4.95</v>
+        <v>5.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.79</v>
+        <v>4.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.75</v>
+        <v>1.19</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>3.33</v>
+        <v>5.4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.75</v>
+        <v>8.9</v>
       </c>
       <c r="O13" t="n">
-        <v>3.9</v>
+        <v>1.65</v>
       </c>
       <c r="P13" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.37</v>
+        <v>6.86</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="V13" t="n">
-        <v>5.55</v>
+        <v>4.95</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>4.79</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.19</v>
+        <v>3.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V19" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="P20" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8</v>
+        <v>3.39</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.14</v>
+        <v>2.76</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.93</v>
+        <v>1.77</v>
       </c>
       <c r="M23" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.72</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4.76</v>
+        <v>2.34</v>
       </c>
       <c r="P23" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.28</v>
+        <v>4.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>2.71</v>
       </c>
       <c r="U23" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.15</v>
+        <v>1.95</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46013.79166666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.77</v>
+        <v>3.93</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>1.72</v>
       </c>
       <c r="O24" t="n">
-        <v>2.34</v>
+        <v>4.76</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.45</v>
+        <v>2.28</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="T24" t="n">
-        <v>2.71</v>
+        <v>2.44</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.95</v>
+        <v>1.15</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46013.89583333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="M4" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="O4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="P4" t="n">
         <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.77</v>
+        <v>4.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
@@ -939,31 +939,31 @@
         <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.17</v>
+        <v>4.27</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
         <v>2.73</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
         <v>1.65</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AG4" t="n">
         <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46013.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.57</v>
+        <v>1.9</v>
       </c>
       <c r="M7" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="N7" t="n">
-        <v>2.03</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.58</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U7" t="n">
         <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>6.6</v>
+        <v>6.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
         <v>1.95</v>
       </c>
       <c r="AC7" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>3.44</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.49</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
         <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T8" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="AA8" t="n">
         <v>1.8</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.34</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>6.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>11.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.91</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>6.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.77</v>
+        <v>2.27</v>
       </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="V11" t="n">
-        <v>6.7</v>
+        <v>4.95</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>4.91</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>3.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>2.91</v>
       </c>
       <c r="P12" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.37</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="V12" t="n">
-        <v>5.55</v>
+        <v>6.7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4</v>
+        <v>3.33</v>
       </c>
       <c r="N13" t="n">
-        <v>8.9</v>
+        <v>1.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.65</v>
+        <v>3.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.86</v>
+        <v>2.37</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="T13" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>4.95</v>
+        <v>5.55</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.79</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.75</v>
+        <v>1.19</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2572,13 +2572,13 @@
         <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2620,10 +2620,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
         <v>2.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.14</v>
+        <v>2.77</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>6.39</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="N2" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="O2" t="n">
         <v>5.5</v>
@@ -674,13 +674,13 @@
         <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="T2" t="n">
         <v>2.27</v>
@@ -689,7 +689,7 @@
         <v>1.52</v>
       </c>
       <c r="V2" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
@@ -698,19 +698,19 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB2" t="n">
         <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="AD2" t="n">
         <v>1.48</v>
@@ -719,13 +719,13 @@
         <v>1.67</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46013.22916666666</v>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="M3" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="N3" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="O3" t="n">
-        <v>5.25</v>
+        <v>4.76</v>
       </c>
       <c r="P3" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
@@ -799,13 +799,13 @@
         <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="T3" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="U3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V3" t="n">
         <v>5.7</v>
@@ -814,16 +814,16 @@
         <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
         <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB3" t="n">
         <v>2.2</v>
@@ -832,19 +832,19 @@
         <v>2.49</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="n">
         <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.06</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46013.375</v>
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>5.43</v>
+        <v>5.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
         <v>2.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="T5" t="n">
         <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
         <v>9.199999999999999</v>
@@ -1055,28 +1055,28 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AD5" t="n">
         <v>1.12</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
         <v>1.27</v>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="M6" t="n">
         <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="O6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
         <v>2.25</v>
@@ -1159,10 +1159,10 @@
         <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
         <v>7</v>
@@ -1177,13 +1177,13 @@
         <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AC6" t="n">
         <v>3.1</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.9</v>
+        <v>4.13</v>
       </c>
       <c r="M7" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.49</v>
+        <v>4.5</v>
       </c>
       <c r="P7" t="n">
         <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T7" t="n">
-        <v>2.43</v>
+        <v>2.77</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O8" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.34</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>3.53</v>
       </c>
       <c r="N9" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.65</v>
       </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.3</v>
+        <v>1.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.15</v>
+        <v>9.65</v>
       </c>
       <c r="O10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH10" t="n">
         <v>3.6</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.34</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.22</v>
       </c>
-      <c r="M11" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="N11" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH11" t="n">
-        <v>3.75</v>
+        <v>1.16</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>6.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>11.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.91</v>
+        <v>1.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>6.86</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.77</v>
+        <v>2.27</v>
       </c>
       <c r="U12" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="V12" t="n">
-        <v>6.7</v>
+        <v>4.95</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.5</v>
+        <v>4.91</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>3.75</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="M13" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>1.75</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.3</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>6.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.25</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
         <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="W14" t="n">
         <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AD14" t="n">
         <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AF14" t="n">
         <v>1.49</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46013.64583333334</v>
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="P15" t="n">
         <v>2.4</v>
@@ -2224,22 +2224,22 @@
         <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
         <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
         <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.05</v>
@@ -2251,13 +2251,13 @@
         <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="AD15" t="n">
         <v>1.3</v>
@@ -2334,13 +2334,13 @@
         <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
         <v>2.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="R16" t="n">
         <v>1.25</v>
@@ -2367,7 +2367,7 @@
         <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA16" t="n">
         <v>1.59</v>
@@ -2382,13 +2382,13 @@
         <v>1.46</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AF16" t="n">
         <v>2.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH16" t="n">
         <v>1.44</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.27</v>
+        <v>4.15</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="O17" t="n">
         <v>4.4</v>
@@ -2465,7 +2465,7 @@
         <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
         <v>2.1</v>
@@ -2507,10 +2507,10 @@
         <v>2.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
         <v>2.25</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.64</v>
+        <v>2.18</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.75</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
         <v>2.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.77</v>
+        <v>3.16</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="P20" t="n">
         <v>2.01</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.14</v>
+        <v>2.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z21" t="n">
         <v>3.85</v>
       </c>
-      <c r="O21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="AA21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.4</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.84</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>3.94</v>
       </c>
       <c r="O22" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.71</v>
+        <v>3.14</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3158,34 +3158,34 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="M23" t="n">
         <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>4.38</v>
       </c>
       <c r="O23" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.45</v>
+        <v>5.14</v>
       </c>
       <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.37</v>
       </c>
       <c r="V23" t="n">
         <v>6.8</v>
@@ -3197,34 +3197,34 @@
         <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AF23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.95</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46013.79166666666</v>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.93</v>
+        <v>4.18</v>
       </c>
       <c r="M24" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="N24" t="n">
         <v>1.72</v>
@@ -3289,22 +3289,22 @@
         <v>4.76</v>
       </c>
       <c r="P24" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="T24" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
         <v>5.6</v>
@@ -3313,31 +3313,31 @@
         <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
         <v>2.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AG24" t="n">
         <v>1.21</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>1.84</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>9.4</v>
+        <v>3.94</v>
       </c>
       <c r="O21" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.64</v>
+        <v>3.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.84</v>
+        <v>1.31</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.94</v>
+        <v>9.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.4</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
         <v>5.5</v>
@@ -1046,7 +1046,7 @@
         <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
@@ -1061,10 +1061,10 @@
         <v>2.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.54</v>
+        <v>2.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
         <v>4.7</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.7</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>6.11</v>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>11.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.37</v>
+        <v>6.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="U11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.5</v>
       </c>
-      <c r="V11" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.16</v>
+        <v>3.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.22</v>
       </c>
-      <c r="M12" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="N12" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH12" t="n">
-        <v>3.75</v>
+        <v>1.16</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1971,10 +1971,10 @@
         <v>2.35</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="O13" t="n">
         <v>2.75</v>
@@ -2004,7 +2004,7 @@
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
         <v>1.24</v>
@@ -2013,7 +2013,7 @@
         <v>3.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB13" t="n">
         <v>1.85</v>
@@ -2087,34 +2087,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>8.550000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="P14" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
         <v>7.4</v>
@@ -2123,37 +2123,37 @@
         <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46013.64583333334</v>
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="M15" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O15" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P15" t="n">
         <v>2.4</v>
@@ -2239,7 +2239,7 @@
         <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.05</v>
@@ -2272,7 +2272,7 @@
         <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46013.65625</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.28</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>2.25</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.78</v>
+        <v>4.75</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
         <v>2.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.16</v>
+        <v>2.77</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.64</v>
+        <v>2.18</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>4.75</v>
+        <v>2.77</v>
       </c>
       <c r="O20" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.43</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.25</v>
       </c>
-      <c r="N21" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.4</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.31</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>9.4</v>
+        <v>3.94</v>
       </c>
       <c r="O22" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="V22" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.64</v>
+        <v>3.14</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="N23" t="n">
-        <v>4.38</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.14</v>
+        <v>4.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="U23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.36</v>
       </c>
-      <c r="V23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46013.79166666666</v>
@@ -3277,28 +3277,28 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O24" t="n">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="T24" t="n">
         <v>2.36</v>
@@ -3319,28 +3319,28 @@
         <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC24" t="n">
         <v>2.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
         <v>1.15</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.13</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
         <v>1.75</v>
@@ -1269,19 +1269,19 @@
         <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="R7" t="n">
         <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T7" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V7" t="n">
         <v>6.4</v>
@@ -1299,10 +1299,10 @@
         <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>3.3</v>
@@ -1311,10 +1311,10 @@
         <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
         <v>2</v>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>9.65</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.65</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="Q10" t="n">
         <v>7.5</v>
@@ -1638,13 +1638,13 @@
         <v>2.05</v>
       </c>
       <c r="U10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
         <v>4.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
@@ -1656,16 +1656,16 @@
         <v>5.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
         <v>1.75</v>
@@ -1677,7 +1677,7 @@
         <v>1.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1733,13 +1733,13 @@
         <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>6.11</v>
+        <v>5.4</v>
       </c>
       <c r="N11" t="n">
-        <v>11.3</v>
+        <v>8.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="P11" t="n">
         <v>2.63</v>
@@ -1760,7 +1760,7 @@
         <v>1.58</v>
       </c>
       <c r="V11" t="n">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="W11" t="n">
         <v>1.12</v>
@@ -1775,16 +1775,16 @@
         <v>4.91</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
         <v>1.95</v>
@@ -1793,10 +1793,10 @@
         <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N12" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
         <v>3.9</v>
@@ -1867,7 +1867,7 @@
         <v>2.37</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
         <v>3.09</v>
@@ -1876,7 +1876,7 @@
         <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
         <v>5.55</v>
@@ -1891,19 +1891,19 @@
         <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AC12" t="n">
         <v>2.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
         <v>1.57</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
         <v>8.300000000000001</v>
@@ -2251,10 +2251,10 @@
         <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AC15" t="n">
         <v>3.05</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N20" t="n">
         <v>3.3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.77</v>
       </c>
       <c r="O20" t="n">
         <v>2.9</v>
@@ -2846,10 +2846,10 @@
         <v>3.16</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>3.55</v>
@@ -2926,7 +2926,7 @@
         <v>5.2</v>
       </c>
       <c r="N21" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="O21" t="n">
         <v>1.77</v>
@@ -2965,10 +2965,10 @@
         <v>4.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC21" t="n">
         <v>2.64</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1025,40 +1025,40 @@
         <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="AA5" t="n">
         <v>2.17</v>
@@ -1067,16 +1067,16 @@
         <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
         <v>1.27</v>
@@ -1135,43 +1135,43 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="M6" t="n">
         <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="P6" t="n">
         <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T6" t="n">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V6" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
         <v>1.25</v>
@@ -1180,16 +1180,16 @@
         <v>3.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
         <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
         <v>1.75</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
         <v>4.5</v>
       </c>
-      <c r="P7" t="n">
+      <c r="T7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE7" t="n">
         <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>1.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>3.68</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,61 +1611,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="P10" t="n">
-        <v>3.01</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.5</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>2.77</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.75</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
         <v>1.75</v>
@@ -1674,10 +1674,10 @@
         <v>1.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.68</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>5.4</v>
+        <v>3.33</v>
       </c>
       <c r="N11" t="n">
-        <v>8.9</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.62</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.9</v>
+        <v>1.16</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>3.33</v>
+        <v>5.4</v>
       </c>
       <c r="N12" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.75</v>
       </c>
-      <c r="O12" t="n">
+      <c r="AG12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH12" t="n">
         <v>3.9</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.16</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
         <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>2.75</v>
@@ -1986,22 +1986,22 @@
         <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>3.09</v>
       </c>
       <c r="T13" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
         <v>6.7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
         <v>1.05</v>
@@ -2013,7 +2013,7 @@
         <v>3.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
         <v>1.85</v>
@@ -2096,22 +2096,22 @@
         <v>6.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S14" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
         <v>1.27</v>
@@ -2126,10 +2126,10 @@
         <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA14" t="n">
         <v>2.21</v>
@@ -2138,22 +2138,22 @@
         <v>1.59</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD14" t="n">
         <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46013.64583333334</v>
@@ -2239,7 +2239,7 @@
         <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.05</v>
@@ -2248,7 +2248,7 @@
         <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA15" t="n">
         <v>1.78</v>
@@ -2269,10 +2269,10 @@
         <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>3</v>
+        <v>1.18</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46013.65625</v>
@@ -2572,40 +2572,40 @@
         <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.5</v>
+        <v>6.04</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA18" t="n">
         <v>2.13</v>
@@ -2614,22 +2614,22 @@
         <v>1.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46013.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.77</v>
+        <v>3.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.3</v>
       </c>
-      <c r="O20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.8</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.16</v>
+        <v>2.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="O21" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>2.77</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="U21" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.64</v>
+        <v>3.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.94</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>2.38</v>
+        <v>1.76</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>6.85</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
         <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.14</v>
+        <v>2.61</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.52</v>
+        <v>26</v>
       </c>
       <c r="M23" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>6.53</v>
       </c>
       <c r="O23" t="n">
         <v>2.22</v>
@@ -3188,7 +3188,7 @@
         <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
         <v>1.11</v>
@@ -3197,10 +3197,10 @@
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
         <v>1.97</v>
@@ -3209,7 +3209,7 @@
         <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD23" t="n">
         <v>1.36</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>1.7</v>
+        <v>63</v>
       </c>
       <c r="O24" t="n">
         <v>4.8</v>
@@ -3307,10 +3307,10 @@
         <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
         <v>1.03</v>
@@ -3322,13 +3322,13 @@
         <v>4.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB24" t="n">
         <v>2.12</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AD24" t="n">
         <v>1.42</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -659,37 +659,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6.39</v>
+        <v>5.3</v>
       </c>
       <c r="M2" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="N2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O2" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="T2" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="U2" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="V2" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
@@ -704,25 +704,25 @@
         <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB2" t="n">
         <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
         <v>1.67</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AH2" t="n">
         <v>1.14</v>
@@ -778,58 +778,58 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="M3" t="n">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="N3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.48</v>
       </c>
-      <c r="O3" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.47</v>
-      </c>
       <c r="V3" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="W3" t="n">
         <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
         <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB3" t="n">
         <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AD3" t="n">
         <v>1.44</v>
@@ -838,13 +838,13 @@
         <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AG3" t="n">
         <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46013.375</v>
@@ -903,43 +903,43 @@
         <v>3.95</v>
       </c>
       <c r="N4" t="n">
-        <v>4.58</v>
+        <v>4.52</v>
       </c>
       <c r="O4" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q4" t="n">
         <v>4.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
         <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V4" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
         <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
         <v>1.67</v>
@@ -948,7 +948,7 @@
         <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="AD4" t="n">
         <v>1.4</v>
@@ -957,13 +957,13 @@
         <v>1.65</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46013.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
         <v>3.3</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="M9" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="O9" t="n">
         <v>2.49</v>
@@ -1513,16 +1513,16 @@
         <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="T9" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V9" t="n">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="W9" t="n">
         <v>1.06</v>
@@ -1531,19 +1531,19 @@
         <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AA9" t="n">
         <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD9" t="n">
         <v>1.36</v>
@@ -1555,10 +1555,10 @@
         <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="T10" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>6.4</v>
+        <v>6.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3.33</v>
+        <v>5.4</v>
       </c>
       <c r="N11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.75</v>
       </c>
-      <c r="O11" t="n">
+      <c r="AG11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH11" t="n">
         <v>3.9</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.16</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>5.4</v>
+        <v>3.33</v>
       </c>
       <c r="N12" t="n">
-        <v>8.9</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.62</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.9</v>
+        <v>1.16</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2.5</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.15</v>
+        <v>2.26</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.68</v>
+        <v>2.52</v>
       </c>
       <c r="O17" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="U17" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2801,31 +2801,31 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>2.38</v>
       </c>
       <c r="P20" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="U20" t="n">
         <v>1.3</v>
@@ -2834,7 +2834,7 @@
         <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
         <v>1.08</v>
@@ -2852,7 +2852,7 @@
         <v>1.69</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AD20" t="n">
         <v>1.2</v>
@@ -2861,13 +2861,13 @@
         <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>1.76</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="V21" t="n">
-        <v>6.85</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
         <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.14</v>
+        <v>2.61</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="U22" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
         <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.61</v>
+        <v>3.14</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -645,7 +645,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -655,7 +655,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -778,37 +778,37 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="M3" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="N3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="O3" t="n">
-        <v>4.52</v>
+        <v>4.94</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
         <v>3.14</v>
       </c>
       <c r="T3" t="n">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="U3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V3" t="n">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="W3" t="n">
         <v>1.08</v>
@@ -820,7 +820,7 @@
         <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA3" t="n">
         <v>1.62</v>
@@ -829,7 +829,7 @@
         <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD3" t="n">
         <v>1.44</v>
@@ -838,7 +838,7 @@
         <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AG3" t="n">
         <v>1.22</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="M4" t="n">
         <v>3.95</v>
@@ -915,43 +915,43 @@
         <v>4.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T4" t="n">
         <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="W4" t="n">
         <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
         <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="AA4" t="n">
         <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="n">
         <v>1.65</v>
@@ -960,10 +960,10 @@
         <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46013.45833333334</v>
@@ -1016,28 +1016,28 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="O5" t="n">
-        <v>5.38</v>
+        <v>5.33</v>
       </c>
       <c r="P5" t="n">
         <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="T5" t="n">
         <v>3.17</v>
@@ -1046,7 +1046,7 @@
         <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
@@ -1055,28 +1055,28 @@
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG5" t="n">
         <v>1.27</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,61 +1254,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="P7" t="n">
-        <v>3.02</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.5</v>
+        <v>2.36</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>2.77</v>
       </c>
       <c r="T7" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.75</v>
+        <v>3.28</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
         <v>1.75</v>
@@ -1317,10 +1317,10 @@
         <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.68</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,61 +1373,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
         <v>4.5</v>
       </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
         <v>1.75</v>
@@ -1436,10 +1436,10 @@
         <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.18</v>
+        <v>3.68</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.55</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.54</v>
       </c>
       <c r="O9" t="n">
         <v>2.49</v>
@@ -1516,7 +1516,7 @@
         <v>2.91</v>
       </c>
       <c r="T9" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="U9" t="n">
         <v>1.43</v>
@@ -1531,7 +1531,7 @@
         <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
         <v>3.8</v>
@@ -1540,7 +1540,7 @@
         <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>2.74</v>
@@ -1558,7 +1558,7 @@
         <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="N10" t="n">
         <v>2.15</v>
@@ -1626,7 +1626,7 @@
         <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
@@ -1641,7 +1641,7 @@
         <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>6.65</v>
+        <v>6.55</v>
       </c>
       <c r="W10" t="n">
         <v>1.05</v>
@@ -1653,7 +1653,7 @@
         <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.7</v>
+        <v>4.11</v>
       </c>
       <c r="AA10" t="n">
         <v>1.82</v>
@@ -1671,7 +1671,7 @@
         <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
         <v>1.7</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>5.4</v>
+        <v>3.33</v>
       </c>
       <c r="N11" t="n">
-        <v>8.9</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.62</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.9</v>
+        <v>1.16</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>3.33</v>
+        <v>5.4</v>
       </c>
       <c r="N12" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.75</v>
       </c>
-      <c r="O12" t="n">
+      <c r="AG12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH12" t="n">
         <v>3.9</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.16</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="O13" t="n">
         <v>2.75</v>
@@ -1986,22 +1986,22 @@
         <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
         <v>3.09</v>
       </c>
       <c r="T13" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.05</v>
@@ -2019,7 +2019,7 @@
         <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
         <v>4.4</v>
@@ -2340,7 +2340,7 @@
         <v>2.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
         <v>1.21</v>
@@ -2349,7 +2349,7 @@
         <v>3.68</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U16" t="n">
         <v>1.7</v>
@@ -2361,31 +2361,31 @@
         <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
         <v>1.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC16" t="n">
         <v>2.12</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="n">
         <v>1.44</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AG16" t="n">
         <v>1.22</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.26</v>
+        <v>2.57</v>
       </c>
       <c r="M17" t="n">
         <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>2.52</v>
+        <v>2.37</v>
       </c>
       <c r="O17" t="n">
         <v>3.1</v>
@@ -2468,16 +2468,16 @@
         <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V17" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
@@ -2486,7 +2486,7 @@
         <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
         <v>1.59</v>
@@ -2495,10 +2495,10 @@
         <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
         <v>1.53</v>
@@ -2507,10 +2507,10 @@
         <v>2.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.82</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>3.99</v>
       </c>
       <c r="O21" t="n">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U21" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.61</v>
+        <v>3.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>2.38</v>
+        <v>1.76</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>6.85</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
         <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.14</v>
+        <v>2.61</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI24"/>
+  <dimension ref="A1:AI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -880,20 +880,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
         <v>5.33</v>
@@ -1061,10 +1061,10 @@
         <v>2.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
         <v>4.5</v>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,76 +1135,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.1</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>6.75</v>
       </c>
       <c r="O6" t="n">
-        <v>5.95</v>
+        <v>2.11</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>8.25</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.77</v>
+        <v>2.29</v>
       </c>
       <c r="T6" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="U6" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="V6" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.6</v>
+        <v>2.49</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>4.45</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>2.47</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.14</v>
+        <v>2.35</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46013.54166666666</v>
+        <v>46013.53125</v>
       </c>
     </row>
     <row r="7">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,76 +1254,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>5.74</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="O7" t="n">
-        <v>4.5</v>
+        <v>6.05</v>
       </c>
       <c r="P7" t="n">
         <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T7" t="n">
-        <v>2.95</v>
+        <v>3.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>6.4</v>
+        <v>6.85</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
         <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46013.58333333334</v>
+        <v>46013.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.65</v>
       </c>
-      <c r="P8" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.68</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>3.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>2.15</v>
       </c>
       <c r="O9" t="n">
-        <v>2.49</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="V9" t="n">
-        <v>6.05</v>
+        <v>6.7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AB9" t="n">
         <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
         <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.4</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>3.48</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.15</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.72</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>2.89</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
-        <v>6.55</v>
+        <v>4.1</v>
       </c>
       <c r="W10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.05</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>3.78</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
         <v>1.75</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>3.09</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46013.625</v>
+        <v>46013.58333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="M12" t="n">
-        <v>5.4</v>
+        <v>6.65</v>
       </c>
       <c r="N12" t="n">
-        <v>8.9</v>
+        <v>11.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.86</v>
+        <v>6.66</v>
       </c>
       <c r="R12" t="n">
         <v>1.25</v>
@@ -1873,49 +1873,49 @@
         <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="U12" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="V12" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.97</v>
+        <v>4.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>2.82</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>2.21</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="T13" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>6.75</v>
+        <v>5.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.34</v>
+        <v>3.82</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.51</v>
+        <v>2.32</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>6.4</v>
+        <v>2.82</v>
       </c>
       <c r="O14" t="n">
-        <v>2.07</v>
+        <v>2.93</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.25</v>
       </c>
-      <c r="U14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.47</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46013.64583333334</v>
+        <v>46013.625</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>9</v>
+        <v>1.51</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>6.4</v>
       </c>
       <c r="O15" t="n">
-        <v>8.300000000000001</v>
+        <v>2.06</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>8.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.81</v>
+        <v>2.41</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.78</v>
+        <v>2.21</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.06</v>
+        <v>2.47</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46013.65625</v>
+        <v>46013.64583333334</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.2</v>
+        <v>9.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="O16" t="n">
-        <v>4.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
         <v>3.68</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6</v>
-      </c>
       <c r="AA16" t="n">
-        <v>1.4</v>
+        <v>1.96</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.12</v>
+        <v>2.94</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46013.66666666666</v>
+        <v>46013.65625</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.57</v>
+        <v>4.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.37</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>3.68</v>
       </c>
       <c r="T17" t="n">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="V17" t="n">
-        <v>5.05</v>
+        <v>4.2</v>
       </c>
       <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.11</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z17" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,76 +2563,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>2.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>2.37</v>
       </c>
       <c r="O18" t="n">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>2.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.04</v>
+        <v>2.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.58</v>
+        <v>3.36</v>
       </c>
       <c r="T18" t="n">
-        <v>3.14</v>
+        <v>2.31</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>8.6</v>
+        <v>5.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.81</v>
+        <v>4.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.13</v>
+        <v>1.59</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="AG18" t="n">
         <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46013.6875</v>
+        <v>46013.66666666666</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,76 +2682,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.5</v>
+        <v>6.03</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.03</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.65</v>
+        <v>3.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46013.70833333334</v>
+        <v>46013.6875</v>
       </c>
     </row>
     <row r="20">
@@ -2801,34 +2801,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="O20" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="P20" t="n">
         <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="T20" t="n">
         <v>3.39</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
         <v>8.5</v>
@@ -2840,31 +2840,31 @@
         <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="AA20" t="n">
         <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AF20" t="n">
         <v>1.68</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
         <v>2</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,76 +2920,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="M21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z21" t="n">
         <v>3.4</v>
       </c>
-      <c r="N21" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB21" t="n">
         <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46013.73958333334</v>
+        <v>46013.70833333334</v>
       </c>
     </row>
     <row r="22">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>3.99</v>
       </c>
       <c r="O22" t="n">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U22" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>5.5</v>
+        <v>6.95</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.61</v>
+        <v>3.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,76 +3158,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>26</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>4.9</v>
       </c>
       <c r="N23" t="n">
-        <v>6.53</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>2.22</v>
+        <v>1.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.2</v>
+        <v>2.61</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46013.79166666666</v>
+        <v>46013.73958333334</v>
       </c>
     </row>
     <row r="24">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,75 +3277,194 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>2.95</v>
       </c>
       <c r="N24" t="n">
-        <v>63</v>
+        <v>6.53</v>
       </c>
       <c r="O24" t="n">
-        <v>4.8</v>
+        <v>2.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.24</v>
+        <v>4.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
         <v>1.03</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AI24" s="3" t="n">
+        <v>46013.79166666666</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Molynes United</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>6</v>
+      </c>
+      <c r="N25" t="n">
+        <v>63</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="Z25" t="n">
         <v>4.15</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AA25" t="n">
         <v>1.62</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AB25" t="n">
         <v>2.12</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AC25" t="n">
         <v>2.52</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AD25" t="n">
         <v>1.42</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AE25" t="n">
         <v>1.59</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AF25" t="n">
         <v>2.17</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AG25" t="n">
         <v>1.2</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AH25" t="n">
         <v>1.15</v>
       </c>
-      <c r="AI24" s="3" t="n">
+      <c r="AI25" s="3" t="n">
         <v>46013.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -999,51 +999,51 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.7</v>
+        <v>3.51</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>5.33</v>
+        <v>4.89</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="R5" t="n">
         <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
         <v>9</v>
@@ -1055,34 +1055,34 @@
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG5" t="n">
         <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46013.52083333334</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>6.75</v>
+        <v>7.35</v>
       </c>
       <c r="O6" t="n">
         <v>2.11</v>
@@ -1180,10 +1180,10 @@
         <v>2.49</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
         <v>4.45</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>3.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>2.15</v>
       </c>
       <c r="O8" t="n">
-        <v>2.49</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="V8" t="n">
-        <v>6.05</v>
+        <v>6.7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AB8" t="n">
         <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AD8" t="n">
         <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.25</v>
+        <v>4.19</v>
       </c>
       <c r="M9" t="n">
         <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>1.94</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>3.36</v>
       </c>
       <c r="O10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.65</v>
       </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.78</v>
+        <v>1.69</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.3</v>
+        <v>1.24</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>8.75</v>
       </c>
       <c r="O11" t="n">
-        <v>4.5</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.35</v>
+        <v>8.75</v>
       </c>
       <c r="R11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="AB11" t="n">
         <v>2.7</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AC11" t="n">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="n">
         <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>3.88</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.19</v>
+        <v>2.32</v>
       </c>
       <c r="M12" t="n">
-        <v>6.65</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>11.8</v>
+        <v>2.82</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>2.93</v>
       </c>
       <c r="P12" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.66</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="T12" t="n">
-        <v>2.21</v>
+        <v>2.69</v>
       </c>
       <c r="U12" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>4.9</v>
+        <v>6.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.7</v>
+        <v>3.42</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.32</v>
+        <v>1.19</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>6.65</v>
       </c>
       <c r="N14" t="n">
-        <v>2.82</v>
+        <v>11.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.93</v>
+        <v>1.67</v>
       </c>
       <c r="P14" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>6.66</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.69</v>
+        <v>2.21</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="V14" t="n">
-        <v>6.55</v>
+        <v>4.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.42</v>
+        <v>4.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>3.75</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46013.625</v>
@@ -2206,31 +2206,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.35</v>
+        <v>8.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
         <v>1.27</v>
@@ -2239,7 +2239,7 @@
         <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1.07</v>
@@ -2248,31 +2248,31 @@
         <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC15" t="n">
         <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46013.64583333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.2</v>
+        <v>2.57</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>2.37</v>
       </c>
       <c r="O17" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.12</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.68</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="V17" t="n">
-        <v>4.2</v>
+        <v>5.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.57</v>
+        <v>4.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.37</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>3.36</v>
+        <v>3.68</v>
       </c>
       <c r="T18" t="n">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="V18" t="n">
-        <v>5.05</v>
+        <v>4.2</v>
       </c>
       <c r="W18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.11</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z18" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2685,34 +2685,34 @@
         <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="P19" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.03</v>
+        <v>5.76</v>
       </c>
       <c r="R19" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S19" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="U19" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W19" t="n">
         <v>1.01</v>
@@ -2727,28 +2727,28 @@
         <v>2.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="AD19" t="n">
         <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="AF19" t="n">
         <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46013.6875</v>
@@ -2920,37 +2920,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="M21" t="n">
         <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="Q21" t="n">
         <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="T21" t="n">
         <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
         <v>1.03</v>
@@ -2974,7 +2974,7 @@
         <v>3.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
         <v>1.67</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="N22" t="n">
-        <v>3.99</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>6.95</v>
+        <v>5.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>8.800000000000001</v>
+        <v>3.99</v>
       </c>
       <c r="O23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.8</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.61</v>
+        <v>3.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>26</v>
+        <v>7.6</v>
       </c>
       <c r="M24" t="n">
-        <v>2.95</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>6.53</v>
+        <v>33</v>
       </c>
       <c r="O24" t="n">
         <v>2.22</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="N25" t="n">
-        <v>63</v>
+        <v>501</v>
       </c>
       <c r="O25" t="n">
         <v>4.8</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.25</v>
+        <v>4.19</v>
       </c>
       <c r="M8" t="n">
         <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.19</v>
+        <v>3.25</v>
       </c>
       <c r="M9" t="n">
         <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.36</v>
       </c>
-      <c r="V9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.19</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,99 +1585,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.36</v>
+        <v>8.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.49</v>
+        <v>1.65</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="Q10" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V10" t="n">
         <v>4</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.8</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.69</v>
+        <v>3.88</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="M11" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>8.75</v>
+        <v>3.36</v>
       </c>
       <c r="O11" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.65</v>
       </c>
-      <c r="P11" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.88</v>
+        <v>1.69</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,99 +1823,99 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>2.82</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.93</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>2.21</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
         <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>6.55</v>
+        <v>5.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,99 +1942,99 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>1.19</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>6.65</v>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>11.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.9</v>
+        <v>1.67</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="Q13" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.21</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2.5</v>
       </c>
-      <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.19</v>
+        <v>3.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46013.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,99 +2061,99 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.19</v>
+        <v>2.32</v>
       </c>
       <c r="M14" t="n">
-        <v>6.65</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>11.8</v>
+        <v>2.82</v>
       </c>
       <c r="O14" t="n">
-        <v>1.67</v>
+        <v>2.93</v>
       </c>
       <c r="P14" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.66</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>2.21</v>
+        <v>2.69</v>
       </c>
       <c r="U14" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>4.9</v>
+        <v>6.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.7</v>
+        <v>3.42</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46013.625</v>
@@ -2189,20 +2189,20 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.57</v>
+        <v>2.42</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="U17" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="V17" t="n">
-        <v>5.05</v>
+        <v>4.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.47</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.2</v>
+        <v>4.95</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="O18" t="n">
         <v>4.4</v>
@@ -2578,25 +2578,25 @@
         <v>2.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
       <c r="T18" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="U18" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="V18" t="n">
         <v>4.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
@@ -2608,10 +2608,10 @@
         <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AC18" t="n">
         <v>2.12</v>
@@ -2629,7 +2629,7 @@
         <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46013.66666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.67</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="AF20" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46013.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.26</v>
+        <v>1.67</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="P21" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S21" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>3.39</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.4</v>
+        <v>2.73</v>
       </c>
       <c r="AA21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH21" t="n">
         <v>2</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46013.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>3.99</v>
       </c>
       <c r="O22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.8</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AC22" t="n">
-        <v>2.61</v>
+        <v>3.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="N23" t="n">
-        <v>3.99</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>6.95</v>
+        <v>5.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46013.73958333334</v>

--- a/jogos_2025-12-22.xlsx
+++ b/jogos_2025-12-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI25"/>
+  <dimension ref="A1:AI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,25 +1347,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.19</v>
+        <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.83</v>
+        <v>8.75</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>1.65</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>8.75</v>
       </c>
       <c r="R8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1.4</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AB8" t="n">
         <v>2.7</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC8" t="n">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.19</v>
+        <v>3.88</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.72</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="U9" t="n">
         <v>1.45</v>
       </c>
       <c r="V9" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AD9" t="n">
         <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1585,99 +1585,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.24</v>
+        <v>4.19</v>
       </c>
       <c r="M10" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>8.75</v>
+        <v>1.83</v>
       </c>
       <c r="O10" t="n">
-        <v>1.65</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.75</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.88</v>
+        <v>1.19</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,25 +1704,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.94</v>
+        <v>3.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.36</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
-        <v>2.49</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
         <v>1.45</v>
       </c>
       <c r="V11" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AD11" t="n">
         <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46013.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,25 +1823,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>2.32</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>2.1</v>
+        <v>2.82</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>2.93</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.21</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="U12" t="n">
         <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>5.9</v>
+        <v>6.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46013.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,99 +2061,99 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
       <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>2.82</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.93</v>
+        <v>3.9</v>
       </c>
       <c r="P14" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>2.21</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="T14" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
         <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>6.55</v>
+        <v>5.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46013.625</v>
@@ -2311,17 +2311,17 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2427,20 +2427,20 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2549,17 +2549,17 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2784,20 +2784,20 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -2903,20 +2903,20 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,99 +3013,99 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.99</v>
+        <v>7</v>
       </c>
       <c r="O22" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="T22" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="V22" t="n">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46013.73958333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,19 +3132,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -3154,318 +3154,80 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>8.800000000000001</v>
+        <v>3.59</v>
       </c>
       <c r="O23" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="P23" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>5.75</v>
+        <v>6.52</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.61</v>
+        <v>3.28</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.9</v>
+        <v>1.78</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46013.73958333334</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46013</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Racing United</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Harbour View</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N24" t="n">
-        <v>33</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AI24" s="3" t="n">
-        <v>46013.79166666666</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46013</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Molynes United</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M25" t="n">
-        <v>21</v>
-      </c>
-      <c r="N25" t="n">
-        <v>501</v>
-      </c>
-      <c r="O25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI25" s="3" t="n">
-        <v>46013.89583333334</v>
       </c>
     </row>
   </sheetData>
